--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:52</t>
+    <t xml:space="preserve">2026-09-24 01:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1079,19 +1079,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.15</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="25">
@@ -1102,19 +1102,19 @@
         <v>34</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.28</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="26">
@@ -1125,19 +1125,19 @@
         <v>34</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.81</v>
+        <v>0.25</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.65</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1.39</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="27">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:41</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2023_coquimbo.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 20:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
